--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdAccountSub002.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdAccountSub002.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\BS-1.9\dev\branches\2.1.0\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="11712" windowHeight="8676"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="11715" windowHeight="8670"/>
   </bookViews>
   <sheets>
     <sheet name="资产池基本信息" sheetId="1" r:id="rId1"/>
@@ -16,13 +21,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>资产池名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>资产池起始日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不能修改模板样式，表头从第2行开始；
+数据填写使用中文名称
+资产池名称样式：文本
+资产池名称内容：中文名称
+资产池名称长度不能大于60个字符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产池起始日期格式：YYYY-MM-DD</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -64,9 +81,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
@@ -89,7 +109,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -131,7 +151,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -166,7 +186,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -375,20 +395,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="37.3984375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="36.09765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="37.375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="36.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="81" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
@@ -403,7 +431,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -414,7 +442,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdAccountSub002.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdAccountSub002.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\BS-1.9\dev\branches\2.1.0\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\产品中债(宁波)\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -56,6 +56,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -81,7 +82,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -89,6 +90,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -399,7 +406,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="37.375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="36.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="36.125" style="4" customWidth="1"/>
     <col min="3" max="3" width="16.125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="2"/>
   </cols>
@@ -408,7 +415,7 @@
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -416,7 +423,7 @@
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
     </row>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdAccountSub002.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdAccountSub002.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\产品中债(宁波)\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="11712" windowHeight="8676"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="11715" windowHeight="8670"/>
   </bookViews>
   <sheets>
     <sheet name="资产池基本信息" sheetId="1" r:id="rId1"/>
@@ -16,13 +21,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>资产池名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>资产池起始日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不能修改模板样式，表头从第2行开始；
+数据填写使用中文名称
+资产池名称样式：文本
+资产池名称内容：中文名称
+资产池名称长度不能大于60个字符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产池起始日期格式：YYYY-MM-DD</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -39,6 +56,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -64,11 +82,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -89,7 +116,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -131,7 +158,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -166,7 +193,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -375,20 +402,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="37.3984375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="36.09765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="37.375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="36.125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="16.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="81" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
@@ -403,7 +438,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -414,7 +449,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
